--- a/guru99_automation/src/test/resources/testdata/FundTrafer.xlsx
+++ b/guru99_automation/src/test/resources/testdata/FundTrafer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\wipro_capstone\guru99_capstone\guru99_automation\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8510DE2A-CD6B-498C-BAD4-FF47E9E51E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6918AE89-10FC-411E-ABD5-CBB59BD0D35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4545" yWindow="1935" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="fundTransferData" sheetId="1" r:id="rId1"/>
@@ -411,10 +411,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>184027</v>
+        <v>184458</v>
       </c>
       <c r="B2">
-        <v>184028</v>
+        <v>184459</v>
       </c>
       <c r="C2">
         <v>50</v>
@@ -428,10 +428,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>184028</v>
+        <v>184459</v>
       </c>
       <c r="B3">
-        <v>184029</v>
+        <v>184460</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>184029</v>
+        <v>184460</v>
       </c>
       <c r="B4">
-        <v>184027</v>
+        <v>184458</v>
       </c>
       <c r="C4">
         <v>20</v>
@@ -462,10 +462,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>184027</v>
+        <v>184458</v>
       </c>
       <c r="B5">
-        <v>184027</v>
+        <v>184458</v>
       </c>
       <c r="C5">
         <v>800</v>
@@ -479,7 +479,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>184029</v>
+        <v>184460</v>
       </c>
       <c r="C6">
         <v>890</v>
@@ -493,7 +493,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7">
-        <v>184028</v>
+        <v>184459</v>
       </c>
       <c r="C7">
         <v>456</v>
@@ -507,10 +507,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>184029</v>
+        <v>184460</v>
       </c>
       <c r="B8">
-        <v>184028</v>
+        <v>184459</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
@@ -521,10 +521,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>184029</v>
+        <v>184460</v>
       </c>
       <c r="B9">
-        <v>184028</v>
+        <v>184459</v>
       </c>
       <c r="C9">
         <v>678</v>
@@ -535,10 +535,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>184027</v>
+        <v>184458</v>
       </c>
       <c r="B10">
-        <v>184028</v>
+        <v>184459</v>
       </c>
       <c r="C10">
         <v>120000</v>
